--- a/dipak/assignments/statistics 2/STATISTICS 2 ASSIGNMENT.xlsx
+++ b/dipak/assignments/statistics 2/STATISTICS 2 ASSIGNMENT.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2aa31bb404222563/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2aa31bb404222563/Desktop/dipak/assignments/statistics 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="8_{D5ED8010-35ED-4B26-A61D-446A79B19F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CBCF670-EE55-4581-B899-C02F3286EACC}"/>
@@ -473,10 +473,10 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="189" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,12 +521,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -776,9 +770,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -838,21 +832,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -861,36 +842,16 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -910,13 +871,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -926,14 +880,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="189" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{BA32F28E-CE12-4CB1-9FC9-40C353ED224E}"/>
@@ -1780,7 +1745,7 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="45"/>
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1793,7 +1758,7 @@
       <c r="B3" s="2">
         <v>72</v>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="45"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
@@ -1804,7 +1769,7 @@
       <c r="B4" s="2">
         <v>91</v>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="45"/>
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1819,7 +1784,7 @@
       <c r="B5" s="2">
         <v>77</v>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="45"/>
       <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1834,7 +1799,7 @@
       <c r="B6" s="2">
         <v>80</v>
       </c>
-      <c r="C6" s="25"/>
+      <c r="C6" s="45"/>
       <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
@@ -1849,7 +1814,7 @@
       <c r="B7" s="2">
         <v>72</v>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="45"/>
       <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
@@ -1864,14 +1829,14 @@
       <c r="B8" s="2">
         <v>46</v>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="45"/>
       <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="3">
         <v>15.970806700560448</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1880,7 +1845,7 @@
       <c r="B9" s="2">
         <v>81</v>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="45"/>
       <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
@@ -1895,7 +1860,7 @@
       <c r="B10" s="2">
         <v>54</v>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="45"/>
       <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
@@ -1910,7 +1875,7 @@
       <c r="B11" s="2">
         <v>83</v>
       </c>
-      <c r="C11" s="25"/>
+      <c r="C11" s="45"/>
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
@@ -1925,7 +1890,7 @@
       <c r="B12" s="2">
         <v>46</v>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="45"/>
       <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
@@ -3149,7 +3114,7 @@
       <c r="F8">
         <v>7846</v>
       </c>
-      <c r="H8" s="37"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -3599,252 +3564,209 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="27" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="F2" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="27"/>
+      <c r="G3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="27" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="28">
         <v>40</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="28">
         <v>63</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="28">
         <v>161</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4">
         <v>13.05</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="28">
         <v>35</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="28">
         <v>59</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="28">
         <v>159</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28" t="s">
+      <c r="F5" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5">
         <v>7.95</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5">
         <v>21.65</v>
       </c>
-      <c r="I5" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="28">
         <v>39</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="28">
         <v>64</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="28">
         <v>163</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="26">
         <v>7.85</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="26">
         <v>19.05</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="26">
         <v>17.850000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="28">
         <v>32</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="28">
         <v>69</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="28">
         <v>165</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="28">
         <v>33</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="28">
         <v>60</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="28">
         <v>160</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="28">
         <v>30</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="28">
         <v>55</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="28">
         <v>155</v>
       </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="28">
         <v>31</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="28">
         <v>61</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="28">
         <v>160</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="28">
         <v>40</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="28">
         <v>65</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="28">
         <v>164</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="28">
         <v>38</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="28">
         <v>69</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="28">
         <v>168</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="28">
         <v>37</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="28">
         <v>70</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="28">
         <v>170</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3862,296 +3784,269 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="26" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="F1" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="39">
         <v>21.2</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="25" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="46">
+      <c r="A3" s="28">
         <v>10</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="28">
         <v>14</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="28">
         <v>38</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3" s="39">
         <v>29</v>
       </c>
-      <c r="H3" s="48">
+      <c r="H3" s="35">
         <v>-11.2</v>
       </c>
-      <c r="I3" s="48">
+      <c r="I3" s="35">
         <v>-15</v>
       </c>
-      <c r="J3" s="48">
+      <c r="J3" s="35">
         <v>9.3999999999999986</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="47">
+      <c r="A4" s="34">
         <v>25</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="34">
         <v>29</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="34">
         <v>27</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="34">
         <v>28.6</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="35">
         <v>3.8000000000000007</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="35">
         <v>0</v>
       </c>
-      <c r="J4" s="48">
+      <c r="J4" s="35">
         <v>-1.6000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="47">
+      <c r="A5" s="34">
         <v>15</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="34">
         <v>33</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="34">
         <v>21</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="7">
         <v>5</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="35">
         <v>-6.1999999999999993</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="35">
         <v>4</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="35">
         <v>-7.6000000000000014</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="47">
+      <c r="A6" s="34">
         <v>23</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="34">
         <v>41</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="34">
         <v>35</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="48">
+      <c r="H6" s="35">
         <v>1.8000000000000007</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="35">
         <v>12</v>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="35">
         <v>6.3999999999999986</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="47">
+      <c r="A7" s="34">
         <v>33</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="34">
         <v>28</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="34">
         <v>22</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="48">
+      <c r="H7" s="35">
         <v>11.8</v>
       </c>
-      <c r="I7" s="48">
+      <c r="I7" s="35">
         <v>-1</v>
       </c>
-      <c r="J7" s="48">
+      <c r="J7" s="35">
         <v>-6.6000000000000014</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="27" t="s">
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="G10" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43" t="s">
+      <c r="E11" s="37"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="43" t="s">
+      <c r="I11" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="27" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+      <c r="A12" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="33">
         <v>64.16</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="G12" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="32">
         <v>64.16</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="32">
         <v>32.96</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="32">
         <v>-26.119999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="38" t="s">
+      <c r="A13" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="33">
         <v>30.6</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="33">
         <v>77.2</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38" t="s">
+      <c r="D13" s="33"/>
+      <c r="G13" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="32">
         <v>30.6</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="32">
         <v>77.2</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="32">
         <v>-17.600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="38">
         <v>-26.119999999999997</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="38">
         <v>-17.600000000000001</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="38">
         <v>46.64</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38" t="s">
+      <c r="G14" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="40">
+      <c r="H14" s="32">
         <v>-26.119999999999997</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="36">
         <v>-17.600000000000001</v>
       </c>
-      <c r="J14" s="49">
+      <c r="J14" s="36">
         <v>46.64</v>
       </c>
     </row>
@@ -4175,286 +4070,240 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="27" t="s">
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="F1" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60" t="s">
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="27" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="57">
+      <c r="A3" s="41">
         <v>44835</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="43">
         <v>9.5399999999999999E-2</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="43">
         <v>9.98E-2</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3" s="43">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="53">
+      <c r="G3">
         <v>6.6849895999999999E-3</v>
       </c>
-      <c r="H3" s="53">
+      <c r="H3">
         <v>3.4547694000000005E-3</v>
       </c>
-      <c r="I3" s="59">
+      <c r="I3" s="26">
         <v>2.5162404E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="57">
+      <c r="A4" s="41">
         <v>44836</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="43">
         <v>3.2800000000000003E-2</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="43">
         <v>4.2950000000000002E-2</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="43">
         <v>5.9200000000000003E-2</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" t="s">
         <v>123</v>
       </c>
-      <c r="G4" s="53">
+      <c r="G4">
         <v>3.4547694000000005E-3</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4">
         <v>1.8764855999999985E-3</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="26">
         <v>1.4883396E-3</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="57">
+      <c r="A5" s="41">
         <v>44837</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="43">
         <v>-6.6299999999999998E-2</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="43">
         <v>1.84E-2</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="43">
         <v>9.3799999999999994E-2</v>
       </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="26">
         <v>2.5162404E-3</v>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="26">
         <v>1.4883396E-3</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="26">
         <v>2.3724776000000002E-3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="57">
+      <c r="A6" s="41">
         <v>44838</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="43">
         <v>7.85E-2</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="43">
         <v>8.2600000000000007E-2</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="43">
         <v>7.2700000000000001E-2</v>
       </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="57">
+      <c r="A7" s="41">
         <v>44839</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="43">
         <v>0.1835</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="43">
         <v>0.1421</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="43">
         <v>0.1956</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60" t="s">
+      <c r="F9" s="27"/>
+      <c r="G9" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="H9" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="27" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="55">
+      <c r="B10" s="2">
         <v>1.25</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53" t="s">
+      <c r="F10" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10">
         <v>8.356236999999999E-3</v>
       </c>
-      <c r="H10" s="53">
+      <c r="H10">
         <v>4.3184617500000005E-3</v>
       </c>
-      <c r="I10" s="53">
+      <c r="I10">
         <v>3.1453004999999999E-3</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="53"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53" t="s">
+      <c r="F11" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11">
         <v>4.3184617500000005E-3</v>
       </c>
-      <c r="H11" s="53">
+      <c r="H11">
         <v>2.3456069999999983E-3</v>
       </c>
-      <c r="I11" s="53">
+      <c r="I11">
         <v>1.8604245E-3</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53" t="s">
+      <c r="F12" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12">
         <v>3.1453004999999999E-3</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12">
         <v>1.8604245E-3</v>
       </c>
-      <c r="I12" s="53">
+      <c r="I12">
         <v>2.9655970000000004E-3</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="53"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="56" t="s">
+      <c r="F14" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="42">
         <v>8.356236999999999E-3</v>
       </c>
-      <c r="H14" s="58">
+      <c r="H14" s="42">
         <v>2.3456069999999987E-3</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14" s="42">
         <v>2.9655969999999986E-3</v>
       </c>
     </row>
